--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$T$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$T$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$T$59</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 5 de setembro de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em domingo, 6 de setembro de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -265,6 +265,21 @@
     <t>FA-12216</t>
   </si>
   <si>
+    <t>BNB - BANCO DO NORDESTE</t>
+  </si>
+  <si>
+    <t>BANCO DO NORDESTE DO BRASIL SA</t>
+  </si>
+  <si>
+    <t>1.8 ATIVUZ | BNB | CONTA RENDIMENTO</t>
+  </si>
+  <si>
+    <t>2.3 AZ | BNB | CONTA RENDIMENTO</t>
+  </si>
+  <si>
+    <t>1.7 ATIVUZ | BNB | CONTA INVESTIMENTO</t>
+  </si>
+  <si>
     <t>JOAO PAULO CONSORCIOS</t>
   </si>
   <si>
@@ -283,28 +298,28 @@
     <t>FA-12034</t>
   </si>
   <si>
+    <t>FA-12227</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
     <t>FA-12249</t>
   </si>
   <si>
-    <t>FA-12227</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>FA-12175</t>
   </si>
   <si>
+    <t>FA-12192</t>
+  </si>
+  <si>
+    <t>FA-12197</t>
+  </si>
+  <si>
     <t>FA-12239</t>
   </si>
   <si>
     <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12197</t>
-  </si>
-  <si>
-    <t>FA-12192</t>
   </si>
   <si>
     <t>FA-12267</t>
@@ -471,7 +486,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -619,7 +634,7 @@
         <v>30</v>
       </c>
       <c r="O6" s="9">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>31</v>
@@ -628,7 +643,7 @@
         <v>30</v>
       </c>
       <c r="R6" s="9">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="S6" s="6" t="s">
         <v>31</v>
@@ -681,7 +696,7 @@
         <v>30</v>
       </c>
       <c r="O7" s="9">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>31</v>
@@ -690,7 +705,7 @@
         <v>30</v>
       </c>
       <c r="R7" s="9">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>31</v>
@@ -743,7 +758,7 @@
         <v>30</v>
       </c>
       <c r="O8" s="9">
-        <v>-61</v>
+        <v>-62</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>31</v>
@@ -752,7 +767,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="S8" s="6" t="s">
         <v>31</v>
@@ -805,7 +820,7 @@
         <v>30</v>
       </c>
       <c r="O9" s="9">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>31</v>
@@ -814,7 +829,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="9">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="S9" s="6" t="s">
         <v>31</v>
@@ -867,7 +882,7 @@
         <v>30</v>
       </c>
       <c r="O10" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>31</v>
@@ -876,7 +891,7 @@
         <v>30</v>
       </c>
       <c r="R10" s="9">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="S10" s="6" t="s">
         <v>31</v>
@@ -929,7 +944,7 @@
         <v>30</v>
       </c>
       <c r="O11" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>31</v>
@@ -938,7 +953,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>31</v>
@@ -991,7 +1006,7 @@
         <v>30</v>
       </c>
       <c r="O12" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>31</v>
@@ -1000,7 +1015,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>31</v>
@@ -1053,7 +1068,7 @@
         <v>30</v>
       </c>
       <c r="O13" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>31</v>
@@ -1062,7 +1077,7 @@
         <v>30</v>
       </c>
       <c r="R13" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>38</v>
@@ -1115,7 +1130,7 @@
         <v>30</v>
       </c>
       <c r="O14" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>31</v>
@@ -1124,7 +1139,7 @@
         <v>30</v>
       </c>
       <c r="R14" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>31</v>
@@ -1177,7 +1192,7 @@
         <v>30</v>
       </c>
       <c r="O15" s="9">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>31</v>
@@ -1186,7 +1201,7 @@
         <v>30</v>
       </c>
       <c r="R15" s="9">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>31</v>
@@ -1239,7 +1254,7 @@
         <v>30</v>
       </c>
       <c r="O16" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>31</v>
@@ -1248,7 +1263,7 @@
         <v>30</v>
       </c>
       <c r="R16" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>31</v>
@@ -1301,7 +1316,7 @@
         <v>30</v>
       </c>
       <c r="O17" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>38</v>
@@ -1310,7 +1325,7 @@
         <v>30</v>
       </c>
       <c r="R17" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>31</v>
@@ -1363,7 +1378,7 @@
         <v>30</v>
       </c>
       <c r="O18" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>38</v>
@@ -1372,7 +1387,7 @@
         <v>30</v>
       </c>
       <c r="R18" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>38</v>
@@ -1425,7 +1440,7 @@
         <v>30</v>
       </c>
       <c r="O19" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>38</v>
@@ -1434,7 +1449,7 @@
         <v>30</v>
       </c>
       <c r="R19" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>38</v>
@@ -1487,7 +1502,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>38</v>
@@ -1496,7 +1511,7 @@
         <v>30</v>
       </c>
       <c r="R20" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>38</v>
@@ -1549,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="O21" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>38</v>
@@ -1558,7 +1573,7 @@
         <v>30</v>
       </c>
       <c r="R21" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>38</v>
@@ -1611,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="O22" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>38</v>
@@ -1620,7 +1635,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>38</v>
@@ -1673,7 +1688,7 @@
         <v>30</v>
       </c>
       <c r="O23" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>38</v>
@@ -1682,7 +1697,7 @@
         <v>30</v>
       </c>
       <c r="R23" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>38</v>
@@ -1735,7 +1750,7 @@
         <v>30</v>
       </c>
       <c r="O24" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>38</v>
@@ -1744,7 +1759,7 @@
         <v>30</v>
       </c>
       <c r="R24" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>38</v>
@@ -1797,7 +1812,7 @@
         <v>30</v>
       </c>
       <c r="O25" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>38</v>
@@ -1806,7 +1821,7 @@
         <v>30</v>
       </c>
       <c r="R25" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>38</v>
@@ -1859,7 +1874,7 @@
         <v>30</v>
       </c>
       <c r="O26" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>38</v>
@@ -1868,7 +1883,7 @@
         <v>30</v>
       </c>
       <c r="R26" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>38</v>
@@ -1921,7 +1936,7 @@
         <v>30</v>
       </c>
       <c r="O27" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>38</v>
@@ -1930,7 +1945,7 @@
         <v>30</v>
       </c>
       <c r="R27" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>38</v>
@@ -1983,7 +1998,7 @@
         <v>30</v>
       </c>
       <c r="O28" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>38</v>
@@ -1992,7 +2007,7 @@
         <v>30</v>
       </c>
       <c r="R28" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>38</v>
@@ -2045,7 +2060,7 @@
         <v>30</v>
       </c>
       <c r="O29" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>38</v>
@@ -2054,7 +2069,7 @@
         <v>30</v>
       </c>
       <c r="R29" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>38</v>
@@ -2107,7 +2122,7 @@
         <v>30</v>
       </c>
       <c r="O30" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>38</v>
@@ -2116,7 +2131,7 @@
         <v>30</v>
       </c>
       <c r="R30" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>38</v>
@@ -2169,7 +2184,7 @@
         <v>30</v>
       </c>
       <c r="O31" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>38</v>
@@ -2178,7 +2193,7 @@
         <v>30</v>
       </c>
       <c r="R31" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>38</v>
@@ -2231,7 +2246,7 @@
         <v>30</v>
       </c>
       <c r="O32" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>38</v>
@@ -2240,7 +2255,7 @@
         <v>30</v>
       </c>
       <c r="R32" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>38</v>
@@ -2293,7 +2308,7 @@
         <v>30</v>
       </c>
       <c r="O33" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>38</v>
@@ -2302,7 +2317,7 @@
         <v>30</v>
       </c>
       <c r="R33" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>38</v>
@@ -2355,7 +2370,7 @@
         <v>30</v>
       </c>
       <c r="O34" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>38</v>
@@ -2364,7 +2379,7 @@
         <v>30</v>
       </c>
       <c r="R34" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>38</v>
@@ -2417,7 +2432,7 @@
         <v>30</v>
       </c>
       <c r="O35" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>38</v>
@@ -2426,7 +2441,7 @@
         <v>30</v>
       </c>
       <c r="R35" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>38</v>
@@ -2479,7 +2494,7 @@
         <v>30</v>
       </c>
       <c r="O36" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>38</v>
@@ -2488,7 +2503,7 @@
         <v>30</v>
       </c>
       <c r="R36" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>38</v>
@@ -2541,7 +2556,7 @@
         <v>30</v>
       </c>
       <c r="O37" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>38</v>
@@ -2550,7 +2565,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>38</v>
@@ -2603,7 +2618,7 @@
         <v>30</v>
       </c>
       <c r="O38" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>38</v>
@@ -2612,7 +2627,7 @@
         <v>30</v>
       </c>
       <c r="R38" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>31</v>
@@ -2632,13 +2647,13 @@
         <v>78</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>26</v>
@@ -2659,13 +2674,13 @@
         <v>46265</v>
       </c>
       <c r="M39" s="8">
-        <v>112.5</v>
+        <v>1.74</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O39" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>38</v>
@@ -2674,7 +2689,7 @@
         <v>30</v>
       </c>
       <c r="R39" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>38</v>
@@ -2688,20 +2703,20 @@
         <v>26</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="G40" s="6" t="s">
         <v>26</v>
       </c>
@@ -2709,7 +2724,7 @@
         <v>26</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J40" s="7">
         <v>46265</v>
@@ -2721,13 +2736,13 @@
         <v>46265</v>
       </c>
       <c r="M40" s="8">
-        <v>180</v>
+        <v>5.11</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O40" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>38</v>
@@ -2736,7 +2751,7 @@
         <v>30</v>
       </c>
       <c r="R40" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>38</v>
@@ -2750,19 +2765,19 @@
         <v>26</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>26</v>
@@ -2783,13 +2798,13 @@
         <v>46265</v>
       </c>
       <c r="M41" s="8">
-        <v>180</v>
+        <v>51.3</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O41" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>38</v>
@@ -2798,7 +2813,7 @@
         <v>30</v>
       </c>
       <c r="R41" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>38</v>
@@ -2809,13 +2824,13 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>25</v>
@@ -2836,22 +2851,22 @@
         <v>29</v>
       </c>
       <c r="J42" s="7">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="K42" s="7">
         <v>46265</v>
       </c>
       <c r="L42" s="7">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="M42" s="8">
-        <v>393.43</v>
+        <v>112.5</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O42" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>38</v>
@@ -2860,7 +2875,7 @@
         <v>30</v>
       </c>
       <c r="R42" s="9">
-        <v>-26</v>
+        <v>-6</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>38</v>
@@ -2871,13 +2886,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>25</v>
@@ -2898,22 +2913,22 @@
         <v>29</v>
       </c>
       <c r="J43" s="7">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="K43" s="7">
         <v>46265</v>
       </c>
       <c r="L43" s="7">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="M43" s="8">
-        <v>530</v>
+        <v>180</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O43" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>38</v>
@@ -2922,10 +2937,10 @@
         <v>30</v>
       </c>
       <c r="R43" s="9">
-        <v>-33</v>
+        <v>-6</v>
       </c>
       <c r="S43" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="T43" s="6" t="s">
         <v>26</v>
@@ -2933,13 +2948,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>25</v>
@@ -2951,10 +2966,10 @@
         <v>27</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="7">
-        <v>46260</v>
+        <v>26</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>29</v>
@@ -2969,13 +2984,13 @@
         <v>46265</v>
       </c>
       <c r="M44" s="8">
-        <v>630</v>
+        <v>180</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O44" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>38</v>
@@ -2984,7 +2999,7 @@
         <v>30</v>
       </c>
       <c r="R44" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>38</v>
@@ -2995,14 +3010,14 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="D45" s="6" t="s">
         <v>25</v>
       </c>
@@ -3013,10 +3028,10 @@
         <v>27</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H45" s="7">
-        <v>46260</v>
+        <v>26</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>29</v>
@@ -3031,13 +3046,13 @@
         <v>46265</v>
       </c>
       <c r="M45" s="8">
-        <v>630</v>
+        <v>180</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O45" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>38</v>
@@ -3046,7 +3061,7 @@
         <v>30</v>
       </c>
       <c r="R45" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>38</v>
@@ -3057,28 +3072,28 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H46" s="7">
-        <v>46260</v>
+        <v>26</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>29</v>
@@ -3093,13 +3108,13 @@
         <v>46265</v>
       </c>
       <c r="M46" s="8">
-        <v>650</v>
+        <v>274.02</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O46" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>38</v>
@@ -3108,7 +3123,7 @@
         <v>30</v>
       </c>
       <c r="R46" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>38</v>
@@ -3119,10 +3134,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>26</v>
@@ -3137,31 +3152,31 @@
         <v>27</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H47" s="7">
-        <v>46260</v>
+        <v>26</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J47" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="K47" s="7">
         <v>46265</v>
       </c>
       <c r="L47" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="M47" s="8">
-        <v>680</v>
+        <v>393.43</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O47" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>38</v>
@@ -3170,7 +3185,7 @@
         <v>30</v>
       </c>
       <c r="R47" s="9">
-        <v>-5</v>
+        <v>-27</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>38</v>
@@ -3181,10 +3196,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>26</v>
@@ -3199,31 +3214,31 @@
         <v>27</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H48" s="7">
-        <v>46260</v>
+        <v>26</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>29</v>
       </c>
       <c r="J48" s="7">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="K48" s="7">
         <v>46265</v>
       </c>
       <c r="L48" s="7">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="M48" s="8">
-        <v>680</v>
+        <v>530</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O48" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>38</v>
@@ -3232,10 +3247,10 @@
         <v>30</v>
       </c>
       <c r="R48" s="9">
-        <v>-5</v>
+        <v>-34</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="T48" s="6" t="s">
         <v>26</v>
@@ -3243,10 +3258,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>26</v>
@@ -3279,13 +3294,13 @@
         <v>46265</v>
       </c>
       <c r="M49" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O49" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>38</v>
@@ -3294,7 +3309,7 @@
         <v>30</v>
       </c>
       <c r="R49" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>38</v>
@@ -3305,10 +3320,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>26</v>
@@ -3329,7 +3344,7 @@
         <v>46260</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J50" s="7">
         <v>46265</v>
@@ -3341,13 +3356,13 @@
         <v>46265</v>
       </c>
       <c r="M50" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O50" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>38</v>
@@ -3356,7 +3371,7 @@
         <v>30</v>
       </c>
       <c r="R50" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>38</v>
@@ -3367,13 +3382,13 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>25</v>
@@ -3388,7 +3403,7 @@
         <v>28</v>
       </c>
       <c r="H51" s="7">
-        <v>46248</v>
+        <v>46260</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>29</v>
@@ -3403,13 +3418,13 @@
         <v>46265</v>
       </c>
       <c r="M51" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O51" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>38</v>
@@ -3418,7 +3433,7 @@
         <v>30</v>
       </c>
       <c r="R51" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>38</v>
@@ -3429,10 +3444,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>26</v>
@@ -3441,7 +3456,7 @@
         <v>25</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>27</v>
@@ -3465,13 +3480,13 @@
         <v>46265</v>
       </c>
       <c r="M52" s="8">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O52" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>38</v>
@@ -3480,7 +3495,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>38</v>
@@ -3491,10 +3506,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>26</v>
@@ -3515,65 +3530,375 @@
         <v>46260</v>
       </c>
       <c r="I53" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J53" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K53" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L53" s="7">
+        <v>46265</v>
+      </c>
+      <c r="M53" s="8">
+        <v>680</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O53" s="9">
+        <v>-6</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R53" s="9">
+        <v>-6</v>
+      </c>
+      <c r="S53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T53" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H54" s="7">
+        <v>46260</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J54" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K54" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L54" s="7">
+        <v>46265</v>
+      </c>
+      <c r="M54" s="8">
+        <v>680</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O54" s="9">
+        <v>-6</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R54" s="9">
+        <v>-6</v>
+      </c>
+      <c r="S54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T54" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H55" s="7">
+        <v>46260</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J55" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K55" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L55" s="7">
+        <v>46265</v>
+      </c>
+      <c r="M55" s="8">
+        <v>680</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O55" s="9">
+        <v>-6</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R55" s="9">
+        <v>-6</v>
+      </c>
+      <c r="S55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T55" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="J53" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K53" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L53" s="7">
-        <v>46265</v>
-      </c>
-      <c r="M53" s="8">
+      <c r="B56" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H56" s="7">
+        <v>46248</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J56" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K56" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L56" s="7">
+        <v>46265</v>
+      </c>
+      <c r="M56" s="8">
+        <v>700</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O56" s="9">
+        <v>-6</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R56" s="9">
+        <v>-6</v>
+      </c>
+      <c r="S56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T56" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H57" s="7">
+        <v>46260</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J57" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K57" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L57" s="7">
+        <v>46265</v>
+      </c>
+      <c r="M57" s="8">
+        <v>700</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O57" s="9">
+        <v>-6</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R57" s="9">
+        <v>-6</v>
+      </c>
+      <c r="S57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T57" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H58" s="7">
+        <v>46260</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J58" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K58" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L58" s="7">
+        <v>46265</v>
+      </c>
+      <c r="M58" s="8">
         <v>1200</v>
       </c>
-      <c r="N53" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O53" s="9">
-        <v>-5</v>
-      </c>
-      <c r="P53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="R53" s="9">
-        <v>-5</v>
-      </c>
-      <c r="S53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="T53" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="54" ht="23" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="12">
-        <f>SUM(M6:M53)</f>
-      </c>
-      <c r="N54" s="10"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="13"/>
-      <c r="S54" s="10"/>
-      <c r="T54" s="10"/>
+      <c r="N58" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O58" s="9">
+        <v>-6</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R58" s="9">
+        <v>-6</v>
+      </c>
+      <c r="S58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T58" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" ht="23" customHeight="1">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="12">
+        <f>SUM(M6:M58)</f>
+      </c>
+      <c r="N59" s="10"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="13"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:T5"/>
